--- a/artfynd/A 26133-2026 artfynd.xlsx
+++ b/artfynd/A 26133-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97649558</v>
+        <v>97649559</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398125.719403235</v>
+        <v>398185</v>
       </c>
       <c r="R2" t="n">
-        <v>6804277.178622738</v>
+        <v>6804197</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,10 +770,112 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97649558</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sälen-Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>398126</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6804277</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>JMN0082 (Calluna AB) NVI. Observatör: Rickard Gustavsson.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Jonas Mattsson, Rickard Gustafsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26133-2026 artfynd.xlsx
+++ b/artfynd/A 26133-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832770</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832769</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832604</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832773</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832612</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832614</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832618</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2003,6 +2063,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832693</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2110,6 +2175,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832715</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,6 +2312,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832678</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832771</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2476,6 +2556,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832597</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832616</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2710,6 +2800,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832724</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2817,6 +2912,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832692</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2924,6 +3024,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832691</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3039,6 +3144,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832709</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832671</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3248,6 +3363,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97649559</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3370,6 +3490,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832589</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3492,6 +3617,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832590</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3614,6 +3744,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832591</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3736,6 +3871,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832592</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3858,6 +3998,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832593</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3965,6 +4110,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832595</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4072,6 +4222,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832599</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4179,6 +4334,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832600</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4286,6 +4446,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4393,6 +4558,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832608</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4500,6 +4670,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832609</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4622,6 +4797,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832613</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4744,6 +4924,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832615</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4851,6 +5036,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832620</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4973,6 +5163,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832674</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5080,6 +5275,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832675</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5187,6 +5387,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832677</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5294,6 +5499,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832682</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5401,6 +5611,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832686</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5508,6 +5723,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832687</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5615,6 +5835,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832688</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5722,6 +5947,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832695</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5829,6 +6059,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5936,6 +6171,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832700</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6043,6 +6283,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832701</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6150,6 +6395,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832702</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6257,6 +6507,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832706</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6364,6 +6619,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832707</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6471,6 +6731,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832713</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6578,6 +6843,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832714</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6685,6 +6955,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832716</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6792,6 +7067,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832717</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6899,6 +7179,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832718</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7006,6 +7291,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832719</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7113,6 +7403,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832721</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7220,6 +7515,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832722</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7327,6 +7627,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832725</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7434,6 +7739,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832774</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7541,6 +7851,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832775</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7648,6 +7963,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832777</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7755,6 +8075,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832780</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7882,6 +8207,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832594</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7989,6 +8319,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832772</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8096,6 +8431,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832683</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8203,6 +8543,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832703</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8305,6 +8650,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97649558</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8426,6 +8776,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832617</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8538,6 +8893,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832601</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8650,6 +9010,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832606</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8762,6 +9127,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832610</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8874,6 +9244,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832685</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8991,6 +9366,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832696</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9103,6 +9483,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832697</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9220,6 +9605,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832704</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9337,6 +9727,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832705</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9449,6 +9844,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832708</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9566,6 +9966,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832710</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9683,6 +10088,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832711</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9800,6 +10210,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832712</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9917,6 +10332,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832776</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10024,6 +10444,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832689</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10140,6 +10565,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832598</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10256,6 +10686,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832603</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10372,6 +10807,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832619</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10488,6 +10928,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832667</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10604,6 +11049,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832668</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10720,6 +11170,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832670</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10836,6 +11291,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832672</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10952,6 +11412,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832673</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11068,6 +11533,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832679</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11184,6 +11654,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832680</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11300,6 +11775,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832781</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11407,6 +11887,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832690</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11514,6 +11999,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832607</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11621,6 +12111,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832611</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11732,6 +12227,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832596</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11839,8 +12339,115 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832720</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>